--- a/artfynd/S 841-2025 artfynd.xlsx
+++ b/artfynd/S 841-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1427,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96752316</v>
+        <v>136954677</v>
       </c>
       <c r="B9" t="n">
-        <v>97983</v>
+        <v>99270</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1438,37 +1438,41 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Storrisberget, Jmt</t>
+          <t>Bygget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541427</v>
+        <v>549806</v>
       </c>
       <c r="R9" t="n">
-        <v>6997008</v>
+        <v>7017587</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1487,17 +1491,17 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Stugun</t>
+          <t>Ragunda</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-09-13</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-09-13</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,37 +1510,38 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Albin Enetjärn</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Albin Enetjärn</t>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>Ecogain</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96752316</t>
+          <t>https://artportalen.se/Sighting/136954677</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96752317</v>
+        <v>136954679</v>
       </c>
       <c r="B10" t="n">
-        <v>97975</v>
+        <v>108116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1544,37 +1549,41 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>224361</v>
+        <v>219933</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Kattfot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Antennaria dioica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>(L.) Gaertn.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Storrisberget, Jmt</t>
+          <t>Bygget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541427</v>
+        <v>549805</v>
       </c>
       <c r="R10" t="n">
-        <v>6997008</v>
+        <v>7017596</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1593,17 +1602,17 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Stugun</t>
+          <t>Ragunda</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-09-13</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-09-13</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1612,37 +1621,38 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Albin Enetjärn</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Albin Enetjärn</t>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>Ecogain</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96752317</t>
+          <t>https://artportalen.se/Sighting/136954679</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>96752324</v>
+        <v>136954682</v>
       </c>
       <c r="B11" t="n">
-        <v>80467</v>
+        <v>108116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,37 +1660,41 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>219933</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kattfot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Antennaria dioica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Gaertn.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Storrisberget, Jmt</t>
+          <t>Bygget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>541580</v>
+        <v>549636</v>
       </c>
       <c r="R11" t="n">
-        <v>6996968</v>
+        <v>7017562</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1699,17 +1713,17 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Stugun</t>
+          <t>Ragunda</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-09-13</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-09-13</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1718,37 +1732,38 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Albin Enetjärn</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Albin Enetjärn</t>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>Ecogain</t>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96752324</t>
+          <t>https://artportalen.se/Sighting/136954682</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>96752068</v>
+        <v>96752316</v>
       </c>
       <c r="B12" t="n">
-        <v>101326</v>
+        <v>97983</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1771,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541588</v>
+        <v>541427</v>
       </c>
       <c r="R12" t="n">
-        <v>6997103</v>
+        <v>6997008</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,12 +1825,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
+          <t>2021-09-13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-09-15</t>
+          <t>2021-09-13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1845,16 +1860,16 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96752068</t>
+          <t>https://artportalen.se/Sighting/96752316</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>96752326</v>
+        <v>96752317</v>
       </c>
       <c r="B13" t="n">
-        <v>101326</v>
+        <v>97975</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1862,21 +1877,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>224361</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1886,10 +1901,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541649</v>
+        <v>541427</v>
       </c>
       <c r="R13" t="n">
-        <v>6996805</v>
+        <v>6997008</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1951,51 +1966,51 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96752326</t>
+          <t>https://artportalen.se/Sighting/96752317</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>62062822</v>
+        <v>96752324</v>
       </c>
       <c r="B14" t="n">
-        <v>92509</v>
+        <v>80467</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>760</v>
+        <v>6463</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lilldigerlemmen, Jmt</t>
+          <t>Storrisberget, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578030</v>
+        <v>541580</v>
       </c>
       <c r="R14" t="n">
-        <v>6981062</v>
+        <v>6996968</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2017,22 +2032,17 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Fors</t>
+          <t>Stugun</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>1992-06-02</t>
+          <t>2021-09-13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1992-06-02</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Uppgift från Kjell Berglin. 92-06-02 Lilldigerlemmen</t>
+          <t>2021-09-13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2047,20 +2057,343 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
+          <t>Albin Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Albin Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96752324</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>96752068</v>
+      </c>
+      <c r="B15" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Storrisberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>541588</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6997103</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2021-09-15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2021-09-15</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Albin Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Albin Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96752068</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>96752326</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Storrisberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>541649</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6996805</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2021-09-13</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2021-09-13</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Albin Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Albin Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96752326</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>62062822</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92509</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>760</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Doftticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Haploporus odorus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lilldigerlemmen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>578030</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6981062</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>1992-06-02</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>1992-06-02</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Uppgift från Kjell Berglin. 92-06-02 Lilldigerlemmen</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
           <t>Lars-Åke Bäckström</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
+      <c r="AX17" t="inlineStr">
         <is>
           <t>Via Lars-Åke Bäckström</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr">
+      <c r="AY17" t="inlineStr">
         <is>
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
+      <c r="AZ17" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/62062822</t>
         </is>
@@ -2081,6 +2414,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 841-2025 artfynd.xlsx
+++ b/artfynd/S 841-2025 artfynd.xlsx
@@ -1430,7 +1430,7 @@
         <v>136954677</v>
       </c>
       <c r="B9" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>136954679</v>
       </c>
       <c r="B10" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>136954682</v>
       </c>
       <c r="B11" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 841-2025 artfynd.xlsx
+++ b/artfynd/S 841-2025 artfynd.xlsx
@@ -1430,7 +1430,7 @@
         <v>136954677</v>
       </c>
       <c r="B9" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>136954679</v>
       </c>
       <c r="B10" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>136954682</v>
       </c>
       <c r="B11" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 841-2025 artfynd.xlsx
+++ b/artfynd/S 841-2025 artfynd.xlsx
@@ -1430,7 +1430,7 @@
         <v>136954677</v>
       </c>
       <c r="B9" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>136954679</v>
       </c>
       <c r="B10" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>136954682</v>
       </c>
       <c r="B11" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 841-2025 artfynd.xlsx
+++ b/artfynd/S 841-2025 artfynd.xlsx
@@ -1430,7 +1430,7 @@
         <v>136954677</v>
       </c>
       <c r="B9" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>136954679</v>
       </c>
       <c r="B10" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>136954682</v>
       </c>
       <c r="B11" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 841-2025 artfynd.xlsx
+++ b/artfynd/S 841-2025 artfynd.xlsx
@@ -1430,7 +1430,7 @@
         <v>136954677</v>
       </c>
       <c r="B9" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>136954679</v>
       </c>
       <c r="B10" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>136954682</v>
       </c>
       <c r="B11" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 841-2025 artfynd.xlsx
+++ b/artfynd/S 841-2025 artfynd.xlsx
@@ -1430,7 +1430,7 @@
         <v>136954677</v>
       </c>
       <c r="B9" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>136954679</v>
       </c>
       <c r="B10" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>136954682</v>
       </c>
       <c r="B11" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 841-2025 artfynd.xlsx
+++ b/artfynd/S 841-2025 artfynd.xlsx
@@ -1430,7 +1430,7 @@
         <v>136954677</v>
       </c>
       <c r="B9" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>136954679</v>
       </c>
       <c r="B10" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>136954682</v>
       </c>
       <c r="B11" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 841-2025 artfynd.xlsx
+++ b/artfynd/S 841-2025 artfynd.xlsx
@@ -1430,7 +1430,7 @@
         <v>136954677</v>
       </c>
       <c r="B9" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>136954679</v>
       </c>
       <c r="B10" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>136954682</v>
       </c>
       <c r="B11" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 841-2025 artfynd.xlsx
+++ b/artfynd/S 841-2025 artfynd.xlsx
@@ -1430,7 +1430,7 @@
         <v>136954677</v>
       </c>
       <c r="B9" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>136954679</v>
       </c>
       <c r="B10" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>136954682</v>
       </c>
       <c r="B11" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 841-2025 artfynd.xlsx
+++ b/artfynd/S 841-2025 artfynd.xlsx
@@ -1430,7 +1430,7 @@
         <v>136954677</v>
       </c>
       <c r="B9" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>136954679</v>
       </c>
       <c r="B10" t="n">
-        <v>108154</v>
+        <v>108158</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>136954682</v>
       </c>
       <c r="B11" t="n">
-        <v>108154</v>
+        <v>108158</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 841-2025 artfynd.xlsx
+++ b/artfynd/S 841-2025 artfynd.xlsx
@@ -1430,7 +1430,7 @@
         <v>136954677</v>
       </c>
       <c r="B9" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>136954679</v>
       </c>
       <c r="B10" t="n">
-        <v>108158</v>
+        <v>108179</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>136954682</v>
       </c>
       <c r="B11" t="n">
-        <v>108158</v>
+        <v>108179</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 841-2025 artfynd.xlsx
+++ b/artfynd/S 841-2025 artfynd.xlsx
@@ -1430,7 +1430,7 @@
         <v>136954677</v>
       </c>
       <c r="B9" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>136954679</v>
       </c>
       <c r="B10" t="n">
-        <v>108179</v>
+        <v>108180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>136954682</v>
       </c>
       <c r="B11" t="n">
-        <v>108179</v>
+        <v>108180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 841-2025 artfynd.xlsx
+++ b/artfynd/S 841-2025 artfynd.xlsx
@@ -1430,7 +1430,7 @@
         <v>136954677</v>
       </c>
       <c r="B9" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>136954679</v>
       </c>
       <c r="B10" t="n">
-        <v>108180</v>
+        <v>108185</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>136954682</v>
       </c>
       <c r="B11" t="n">
-        <v>108180</v>
+        <v>108185</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 841-2025 artfynd.xlsx
+++ b/artfynd/S 841-2025 artfynd.xlsx
@@ -1430,7 +1430,7 @@
         <v>136954677</v>
       </c>
       <c r="B9" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>136954679</v>
       </c>
       <c r="B10" t="n">
-        <v>108185</v>
+        <v>108188</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>136954682</v>
       </c>
       <c r="B11" t="n">
-        <v>108185</v>
+        <v>108188</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 841-2025 artfynd.xlsx
+++ b/artfynd/S 841-2025 artfynd.xlsx
@@ -1430,7 +1430,7 @@
         <v>136954677</v>
       </c>
       <c r="B9" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>136954679</v>
       </c>
       <c r="B10" t="n">
-        <v>108188</v>
+        <v>108194</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>136954682</v>
       </c>
       <c r="B11" t="n">
-        <v>108188</v>
+        <v>108194</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 841-2025 artfynd.xlsx
+++ b/artfynd/S 841-2025 artfynd.xlsx
@@ -1541,7 +1541,7 @@
         <v>136954679</v>
       </c>
       <c r="B10" t="n">
-        <v>108194</v>
+        <v>108195</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>136954682</v>
       </c>
       <c r="B11" t="n">
-        <v>108194</v>
+        <v>108195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 841-2025 artfynd.xlsx
+++ b/artfynd/S 841-2025 artfynd.xlsx
@@ -1430,7 +1430,7 @@
         <v>136954677</v>
       </c>
       <c r="B9" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>136954679</v>
       </c>
       <c r="B10" t="n">
-        <v>108195</v>
+        <v>108207</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>136954682</v>
       </c>
       <c r="B11" t="n">
-        <v>108195</v>
+        <v>108207</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 841-2025 artfynd.xlsx
+++ b/artfynd/S 841-2025 artfynd.xlsx
@@ -1430,7 +1430,7 @@
         <v>136954677</v>
       </c>
       <c r="B9" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>136954679</v>
       </c>
       <c r="B10" t="n">
-        <v>108207</v>
+        <v>108208</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>136954682</v>
       </c>
       <c r="B11" t="n">
-        <v>108207</v>
+        <v>108208</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 841-2025 artfynd.xlsx
+++ b/artfynd/S 841-2025 artfynd.xlsx
@@ -1430,7 +1430,7 @@
         <v>136954677</v>
       </c>
       <c r="B9" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>136954679</v>
       </c>
       <c r="B10" t="n">
-        <v>108208</v>
+        <v>108211</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>136954682</v>
       </c>
       <c r="B11" t="n">
-        <v>108208</v>
+        <v>108211</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 841-2025 artfynd.xlsx
+++ b/artfynd/S 841-2025 artfynd.xlsx
@@ -1430,7 +1430,7 @@
         <v>136954677</v>
       </c>
       <c r="B9" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>136954679</v>
       </c>
       <c r="B10" t="n">
-        <v>108211</v>
+        <v>108213</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>136954682</v>
       </c>
       <c r="B11" t="n">
-        <v>108211</v>
+        <v>108213</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 841-2025 artfynd.xlsx
+++ b/artfynd/S 841-2025 artfynd.xlsx
@@ -1430,7 +1430,7 @@
         <v>136954677</v>
       </c>
       <c r="B9" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>136954679</v>
       </c>
       <c r="B10" t="n">
-        <v>108213</v>
+        <v>108217</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>136954682</v>
       </c>
       <c r="B11" t="n">
-        <v>108213</v>
+        <v>108217</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
